--- a/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84816732-85CE-449A-BB99-0BAE7EBEF3FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363B359B-1149-482F-81E2-BCB55CD9505B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DCA29C3-7B4E-4E79-B6A1-CCB19600262D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13ED1F16-AA34-4ABA-A54E-EED8A51EF238}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10EABF77-BFFF-48E2-AAD0-48697B1CA754}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F0EAA5C-4F18-4CF0-90FC-6E7714E6E97D}"/>
 </file>